--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B4" t="n">
-        <v>91539</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R4" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R5" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372423</v>
+        <v>129372443</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474265</v>
+        <v>474197</v>
       </c>
       <c r="R6" t="n">
-        <v>6920708</v>
+        <v>6920850</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372443</v>
+        <v>129372423</v>
       </c>
       <c r="B7" t="n">
-        <v>98688</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474197</v>
+        <v>474265</v>
       </c>
       <c r="R7" t="n">
-        <v>6920850</v>
+        <v>6920708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92243</v>
+        <v>92257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,46 +1369,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B9" t="n">
-        <v>98688</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1420,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R9" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1452,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1461,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1488,38 +1479,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1531,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R10" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1570,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1711,45 +1711,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1800,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,61 +1830,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B13" t="n">
-        <v>98688</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R13" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,18 +1903,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129372422</v>
+        <v>129372419</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474226</v>
+        <v>474177</v>
       </c>
       <c r="R15" t="n">
-        <v>6920695</v>
+        <v>6920810</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129372419</v>
+        <v>129372422</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474177</v>
+        <v>474226</v>
       </c>
       <c r="R16" t="n">
-        <v>6920810</v>
+        <v>6920695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98688</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98688</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98688</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R4" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R5" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372443</v>
+        <v>129372423</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474197</v>
+        <v>474265</v>
       </c>
       <c r="R6" t="n">
-        <v>6920850</v>
+        <v>6920708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372423</v>
+        <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474265</v>
+        <v>474197</v>
       </c>
       <c r="R7" t="n">
-        <v>6920708</v>
+        <v>6920850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,46 +1479,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372446</v>
+        <v>129372439</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474291</v>
+        <v>474241</v>
       </c>
       <c r="R10" t="n">
-        <v>6920735</v>
+        <v>6920840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,18 +1568,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,46 +1592,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372439</v>
+        <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>57831</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1649,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474241</v>
+        <v>474291</v>
       </c>
       <c r="R11" t="n">
-        <v>6920840</v>
+        <v>6920735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,12 +1681,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,61 +1711,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R12" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,18 +1784,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,45 +1808,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R13" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1897,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B4" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R4" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R5" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372423</v>
+        <v>129372443</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474265</v>
+        <v>474197</v>
       </c>
       <c r="R6" t="n">
-        <v>6920708</v>
+        <v>6920850</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372443</v>
+        <v>129372423</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474197</v>
+        <v>474265</v>
       </c>
       <c r="R7" t="n">
-        <v>6920850</v>
+        <v>6920708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1595,7 +1595,7 @@
         <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,45 +1711,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1800,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,61 +1830,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R13" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,18 +1903,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R22" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R23" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129372447</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372443</v>
+        <v>129372423</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474197</v>
+        <v>474265</v>
       </c>
       <c r="R6" t="n">
-        <v>6920850</v>
+        <v>6920708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372423</v>
+        <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474265</v>
+        <v>474197</v>
       </c>
       <c r="R7" t="n">
-        <v>6920708</v>
+        <v>6920850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,61 +1711,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R12" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,18 +1784,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,45 +1808,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R13" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1897,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,7 +2952,7 @@
         <v>129372437</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1369,38 +1369,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372433</v>
+        <v>129372439</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1412,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474231</v>
+        <v>474241</v>
       </c>
       <c r="R9" t="n">
-        <v>6920694</v>
+        <v>6920840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,11 +1456,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,46 +1482,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372439</v>
+        <v>129372446</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1530,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474241</v>
+        <v>474291</v>
       </c>
       <c r="R10" t="n">
-        <v>6920840</v>
+        <v>6920735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1571,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1592,46 +1601,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1643,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R11" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,7 +1684,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,7 +1693,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,45 +1711,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1800,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,61 +1830,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R13" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,18 +1903,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R4" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B5" t="n">
-        <v>91539</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R5" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>129372446</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,61 +1711,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R12" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,18 +1784,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,45 +1808,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R13" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1897,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R22" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R23" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,7 +2952,7 @@
         <v>129372437</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,46 +1369,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372439</v>
+        <v>129372433</v>
       </c>
       <c r="B9" t="n">
-        <v>57831</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1420,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474241</v>
+        <v>474231</v>
       </c>
       <c r="R9" t="n">
-        <v>6920840</v>
+        <v>6920694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,6 +1448,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1482,46 +1479,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372446</v>
+        <v>129372439</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1533,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474291</v>
+        <v>474241</v>
       </c>
       <c r="R10" t="n">
-        <v>6920735</v>
+        <v>6920840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,18 +1568,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,38 +1592,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1644,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R11" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,7 +1683,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,6 +1692,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R4" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R5" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372445</v>
+        <v>129372441</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474362</v>
+        <v>474236</v>
       </c>
       <c r="R20" t="n">
-        <v>6920913</v>
+        <v>6920883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372441</v>
+        <v>129372445</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474236</v>
+        <v>474362</v>
       </c>
       <c r="R21" t="n">
-        <v>6920883</v>
+        <v>6920913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R4" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B5" t="n">
-        <v>91546</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R5" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2233,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129372421</v>
+        <v>129372432</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474223</v>
+        <v>474398</v>
       </c>
       <c r="R17" t="n">
-        <v>6920680</v>
+        <v>6921134</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129372432</v>
+        <v>129372421</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474398</v>
+        <v>474223</v>
       </c>
       <c r="R18" t="n">
-        <v>6921134</v>
+        <v>6920680</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372441</v>
+        <v>129372445</v>
       </c>
       <c r="B20" t="n">
         <v>98724</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474236</v>
+        <v>474362</v>
       </c>
       <c r="R20" t="n">
-        <v>6920883</v>
+        <v>6920913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372445</v>
+        <v>129372441</v>
       </c>
       <c r="B21" t="n">
         <v>98724</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474362</v>
+        <v>474236</v>
       </c>
       <c r="R21" t="n">
-        <v>6920913</v>
+        <v>6920883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R22" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R23" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2233,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129372432</v>
+        <v>129372421</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474398</v>
+        <v>474223</v>
       </c>
       <c r="R17" t="n">
-        <v>6921134</v>
+        <v>6920680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129372421</v>
+        <v>129372432</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474223</v>
+        <v>474398</v>
       </c>
       <c r="R18" t="n">
-        <v>6920680</v>
+        <v>6921134</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,38 +1369,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372433</v>
+        <v>129372439</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1412,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474231</v>
+        <v>474241</v>
       </c>
       <c r="R9" t="n">
-        <v>6920694</v>
+        <v>6920840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,11 +1456,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,46 +1482,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372439</v>
+        <v>129372433</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1530,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474241</v>
+        <v>474231</v>
       </c>
       <c r="R10" t="n">
-        <v>6920840</v>
+        <v>6920694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,7 +1595,7 @@
         <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1369,46 +1369,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372439</v>
+        <v>129372446</v>
       </c>
       <c r="B9" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474241</v>
+        <v>474291</v>
       </c>
       <c r="R9" t="n">
-        <v>6920840</v>
+        <v>6920735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,12 +1458,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1592,46 +1598,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372446</v>
+        <v>129372439</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>57831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1643,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474291</v>
+        <v>474241</v>
       </c>
       <c r="R11" t="n">
-        <v>6920735</v>
+        <v>6920840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,18 +1687,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,45 +1711,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1800,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,61 +1830,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R13" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,18 +1903,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372445</v>
+        <v>129372441</v>
       </c>
       <c r="B20" t="n">
         <v>98727</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474362</v>
+        <v>474236</v>
       </c>
       <c r="R20" t="n">
-        <v>6920913</v>
+        <v>6920883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372441</v>
+        <v>129372445</v>
       </c>
       <c r="B21" t="n">
         <v>98727</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474236</v>
+        <v>474362</v>
       </c>
       <c r="R21" t="n">
-        <v>6920883</v>
+        <v>6920913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R22" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R23" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R4" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R5" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372423</v>
+        <v>129372443</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474265</v>
+        <v>474197</v>
       </c>
       <c r="R6" t="n">
-        <v>6920708</v>
+        <v>6920850</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372443</v>
+        <v>129372423</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474197</v>
+        <v>474265</v>
       </c>
       <c r="R7" t="n">
-        <v>6920850</v>
+        <v>6920708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,46 +1369,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1420,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R9" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1452,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1461,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1488,38 +1479,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1531,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R10" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1570,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1711,61 +1711,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R12" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,18 +1784,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,45 +1808,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R13" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1897,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372441</v>
+        <v>129372445</v>
       </c>
       <c r="B20" t="n">
         <v>98727</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474236</v>
+        <v>474362</v>
       </c>
       <c r="R20" t="n">
-        <v>6920883</v>
+        <v>6920913</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372445</v>
+        <v>129372441</v>
       </c>
       <c r="B21" t="n">
         <v>98727</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474362</v>
+        <v>474236</v>
       </c>
       <c r="R21" t="n">
-        <v>6920913</v>
+        <v>6920883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1369,38 +1369,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372433</v>
+        <v>129372439</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1412,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474231</v>
+        <v>474241</v>
       </c>
       <c r="R9" t="n">
-        <v>6920694</v>
+        <v>6920840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,11 +1456,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,46 +1601,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372439</v>
+        <v>129372433</v>
       </c>
       <c r="B11" t="n">
-        <v>57831</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1649,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474241</v>
+        <v>474231</v>
       </c>
       <c r="R11" t="n">
-        <v>6920840</v>
+        <v>6920694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,6 +1680,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2029,7 +2029,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129372419</v>
+        <v>129372422</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474177</v>
+        <v>474226</v>
       </c>
       <c r="R15" t="n">
-        <v>6920810</v>
+        <v>6920695</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129372422</v>
+        <v>129372419</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474226</v>
+        <v>474177</v>
       </c>
       <c r="R16" t="n">
-        <v>6920695</v>
+        <v>6920810</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R4" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R5" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372443</v>
+        <v>129372423</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474197</v>
+        <v>474265</v>
       </c>
       <c r="R6" t="n">
-        <v>6920850</v>
+        <v>6920708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372423</v>
+        <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474265</v>
+        <v>474197</v>
       </c>
       <c r="R7" t="n">
-        <v>6920708</v>
+        <v>6920850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1482,46 +1482,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1533,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R10" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,7 +1565,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1582,7 +1574,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,38 +1592,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1644,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R11" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,7 +1683,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,6 +1692,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,45 +1711,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1800,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,61 +1830,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R13" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,18 +1903,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129372422</v>
+        <v>129372419</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474226</v>
+        <v>474177</v>
       </c>
       <c r="R15" t="n">
-        <v>6920695</v>
+        <v>6920810</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129372419</v>
+        <v>129372422</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474177</v>
+        <v>474226</v>
       </c>
       <c r="R16" t="n">
-        <v>6920810</v>
+        <v>6920695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R22" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R23" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R4" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R5" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1369,46 +1369,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372439</v>
+        <v>129372446</v>
       </c>
       <c r="B9" t="n">
-        <v>57831</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474241</v>
+        <v>474291</v>
       </c>
       <c r="R9" t="n">
-        <v>6920840</v>
+        <v>6920735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,12 +1458,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1592,46 +1598,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372446</v>
+        <v>129372439</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>57831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1643,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474291</v>
+        <v>474241</v>
       </c>
       <c r="R11" t="n">
-        <v>6920735</v>
+        <v>6920840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,18 +1687,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129372424</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129372418</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372420</v>
+        <v>129372447</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474211</v>
+        <v>474144</v>
       </c>
       <c r="R4" t="n">
-        <v>6920575</v>
+        <v>6920595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372447</v>
+        <v>129372420</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474144</v>
+        <v>474211</v>
       </c>
       <c r="R5" t="n">
-        <v>6920595</v>
+        <v>6920575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>129372423</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129372443</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129372417</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,46 +1369,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>57890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1420,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R9" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1452,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1461,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1488,38 +1479,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372433</v>
+        <v>129372439</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1531,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474231</v>
+        <v>474241</v>
       </c>
       <c r="R10" t="n">
-        <v>6920694</v>
+        <v>6920840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,11 +1566,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,46 +1592,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372439</v>
+        <v>129372446</v>
       </c>
       <c r="B11" t="n">
-        <v>57831</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1649,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474241</v>
+        <v>474291</v>
       </c>
       <c r="R11" t="n">
-        <v>6920840</v>
+        <v>6920735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,12 +1681,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,61 +1711,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R12" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,18 +1784,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,45 +1808,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R13" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,12 +1897,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>129372425</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129372419</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>129372422</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129372421</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>129372432</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>129372444</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>129372445</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129372441</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372426</v>
+        <v>129372438</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474347</v>
+        <v>474241</v>
       </c>
       <c r="R22" t="n">
-        <v>6921012</v>
+        <v>6920718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372438</v>
+        <v>129372426</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474347</v>
       </c>
       <c r="R23" t="n">
-        <v>6920718</v>
+        <v>6921012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,7 +2952,7 @@
         <v>129372437</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1711,45 +1711,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,12 +1800,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1808,61 +1830,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R13" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,18 +1903,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129372424</v>
+        <v>129372418</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>92305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474312</v>
+        <v>474395</v>
       </c>
       <c r="R2" t="n">
-        <v>6920684</v>
+        <v>6921132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129372418</v>
+        <v>129372447</v>
       </c>
       <c r="B3" t="n">
-        <v>92299</v>
+        <v>91583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474395</v>
+        <v>474144</v>
       </c>
       <c r="R3" t="n">
-        <v>6921132</v>
+        <v>6920595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372447</v>
+        <v>129372443</v>
       </c>
       <c r="B4" t="n">
-        <v>91577</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474144</v>
+        <v>474197</v>
       </c>
       <c r="R4" t="n">
-        <v>6920595</v>
+        <v>6920850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372420</v>
+        <v>129372417</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>92305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474211</v>
+        <v>474246</v>
       </c>
       <c r="R5" t="n">
-        <v>6920575</v>
+        <v>6920927</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372423</v>
+        <v>129372433</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474265</v>
+        <v>474231</v>
       </c>
       <c r="R6" t="n">
-        <v>6920708</v>
+        <v>6920694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1146,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,45 +1173,61 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372443</v>
+        <v>129372439</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>57839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474197</v>
+        <v>474241</v>
       </c>
       <c r="R7" t="n">
-        <v>6920850</v>
+        <v>6920840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,45 +1286,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372417</v>
+        <v>129372446</v>
       </c>
       <c r="B8" t="n">
-        <v>92299</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474246</v>
+        <v>474291</v>
       </c>
       <c r="R8" t="n">
-        <v>6920927</v>
+        <v>6920735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,12 +1375,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372433</v>
+        <v>129372436</v>
       </c>
       <c r="B9" t="n">
-        <v>57890</v>
+        <v>80180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,42 +1416,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474231</v>
+        <v>474140</v>
       </c>
       <c r="R9" t="n">
-        <v>6920694</v>
+        <v>6920856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,11 +1476,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,46 +1502,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372439</v>
+        <v>129372442</v>
       </c>
       <c r="B10" t="n">
-        <v>57834</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1530,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474241</v>
+        <v>474194</v>
       </c>
       <c r="R10" t="n">
-        <v>6920840</v>
+        <v>6920828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1591,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1592,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372446</v>
+        <v>129372444</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474291</v>
+        <v>474195</v>
       </c>
       <c r="R11" t="n">
-        <v>6920735</v>
+        <v>6920866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372442</v>
+        <v>129372445</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,33 +1768,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>474362</v>
       </c>
       <c r="R12" t="n">
-        <v>6920828</v>
+        <v>6920913</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,18 +1813,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1830,32 +1837,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372436</v>
+        <v>129372441</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474140</v>
+        <v>474236</v>
       </c>
       <c r="R13" t="n">
-        <v>6920856</v>
+        <v>6920883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129372425</v>
+        <v>129372438</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474348</v>
+        <v>474241</v>
       </c>
       <c r="R14" t="n">
-        <v>6920993</v>
+        <v>6920718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129372419</v>
+        <v>129372437</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474177</v>
+        <v>474157</v>
       </c>
       <c r="R15" t="n">
-        <v>6920810</v>
+        <v>6920662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,11 +2102,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129372422</v>
+        <v>129372424</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474226</v>
+        <v>474312</v>
       </c>
       <c r="R16" t="n">
-        <v>6920695</v>
+        <v>6920684</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129372421</v>
+        <v>129372420</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474223</v>
+        <v>474211</v>
       </c>
       <c r="R17" t="n">
-        <v>6920680</v>
+        <v>6920575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2305,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129372432</v>
+        <v>129372423</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474398</v>
+        <v>474265</v>
       </c>
       <c r="R18" t="n">
-        <v>6921134</v>
+        <v>6920708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,61 +2434,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129372444</v>
+        <v>129372425</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474195</v>
+        <v>474348</v>
       </c>
       <c r="R19" t="n">
-        <v>6920866</v>
+        <v>6920993</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,7 +2509,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,7 +2518,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2556,32 +2536,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372445</v>
+        <v>129372419</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474362</v>
+        <v>474177</v>
       </c>
       <c r="R20" t="n">
-        <v>6920913</v>
+        <v>6920810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,32 +2638,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372441</v>
+        <v>129372422</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474236</v>
+        <v>474226</v>
       </c>
       <c r="R21" t="n">
-        <v>6920883</v>
+        <v>6920695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,6 +2709,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372438</v>
+        <v>129372421</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474241</v>
+        <v>474223</v>
       </c>
       <c r="R22" t="n">
-        <v>6920718</v>
+        <v>6920680</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2811,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372426</v>
+        <v>129372432</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474347</v>
+        <v>474398</v>
       </c>
       <c r="R23" t="n">
-        <v>6921012</v>
+        <v>6921134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2917,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2949,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129372437</v>
+        <v>129372426</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474157</v>
+        <v>474347</v>
       </c>
       <c r="R24" t="n">
-        <v>6920662</v>
+        <v>6921012</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,6 +3015,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129372418</v>
       </c>
       <c r="B2" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129372447</v>
       </c>
       <c r="B3" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129372443</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129372417</v>
       </c>
       <c r="B5" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129372433</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,46 +1173,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372439</v>
+        <v>129372446</v>
       </c>
       <c r="B7" t="n">
-        <v>57839</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474241</v>
+        <v>474291</v>
       </c>
       <c r="R7" t="n">
-        <v>6920840</v>
+        <v>6920735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,12 +1262,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1286,46 +1292,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372446</v>
+        <v>129372439</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>57840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1337,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474291</v>
+        <v>474241</v>
       </c>
       <c r="R8" t="n">
-        <v>6920735</v>
+        <v>6920840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,18 +1381,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,45 +1405,61 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B9" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R9" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,12 +1494,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1502,61 +1524,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R10" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,18 +1597,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>129372444</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129372445</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129372441</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129372438</v>
       </c>
       <c r="B14" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129372437</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129372424</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>129372420</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>129372423</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129372425</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>129372419</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>129372422</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>129372421</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>129372432</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>129372426</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1063,38 +1063,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372433</v>
+        <v>129372439</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1106,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474231</v>
+        <v>474241</v>
       </c>
       <c r="R6" t="n">
-        <v>6920694</v>
+        <v>6920840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1150,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,46 +1295,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372439</v>
+        <v>129372433</v>
       </c>
       <c r="B8" t="n">
-        <v>57840</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1343,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474241</v>
+        <v>474231</v>
       </c>
       <c r="R8" t="n">
-        <v>6920840</v>
+        <v>6920694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,6 +1374,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129372418</v>
       </c>
       <c r="B2" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129372447</v>
       </c>
       <c r="B3" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129372443</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129372417</v>
       </c>
       <c r="B5" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,46 +1063,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372439</v>
+        <v>129372433</v>
       </c>
       <c r="B6" t="n">
-        <v>57840</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1114,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474241</v>
+        <v>474231</v>
       </c>
       <c r="R6" t="n">
-        <v>6920840</v>
+        <v>6920694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,46 +1173,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372446</v>
+        <v>129372439</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>57840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1227,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474291</v>
+        <v>474241</v>
       </c>
       <c r="R7" t="n">
-        <v>6920735</v>
+        <v>6920840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,18 +1262,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,38 +1286,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1338,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R8" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,6 +1386,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,61 +1405,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372442</v>
+        <v>129372436</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474194</v>
+        <v>474140</v>
       </c>
       <c r="R9" t="n">
-        <v>6920828</v>
+        <v>6920856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,18 +1478,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,45 +1502,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372436</v>
+        <v>129372442</v>
       </c>
       <c r="B10" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474140</v>
+        <v>474194</v>
       </c>
       <c r="R10" t="n">
-        <v>6920856</v>
+        <v>6920828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1591,18 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>129372444</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129372445</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>129372441</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129372438</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129372437</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1063,38 +1063,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1106,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R6" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,7 +1154,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1155,6 +1163,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1286,46 +1295,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1337,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R8" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1378,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,7 +1387,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -1063,46 +1063,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372446</v>
+        <v>129372433</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1114,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474291</v>
+        <v>474231</v>
       </c>
       <c r="R6" t="n">
-        <v>6920735</v>
+        <v>6920694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,7 +1146,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1163,7 +1155,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1295,38 +1286,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372433</v>
+        <v>129372446</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1338,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474231</v>
+        <v>474291</v>
       </c>
       <c r="R8" t="n">
-        <v>6920694</v>
+        <v>6920735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,6 +1386,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2131,7 +2131,7 @@
         <v>129372424</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>129372420</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>129372423</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129372425</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372419</v>
+        <v>129372422</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474177</v>
+        <v>474226</v>
       </c>
       <c r="R20" t="n">
-        <v>6920810</v>
+        <v>6920695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372422</v>
+        <v>129372419</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474226</v>
+        <v>474177</v>
       </c>
       <c r="R21" t="n">
-        <v>6920695</v>
+        <v>6920810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372421</v>
+        <v>129372432</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474223</v>
+        <v>474398</v>
       </c>
       <c r="R22" t="n">
-        <v>6920680</v>
+        <v>6921134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372432</v>
+        <v>129372421</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474398</v>
+        <v>474223</v>
       </c>
       <c r="R23" t="n">
-        <v>6921134</v>
+        <v>6920680</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
         <v>129372426</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2131,7 +2131,7 @@
         <v>129372424</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>129372420</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>129372423</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129372425</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372422</v>
+        <v>129372419</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474226</v>
+        <v>474177</v>
       </c>
       <c r="R20" t="n">
-        <v>6920695</v>
+        <v>6920810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372419</v>
+        <v>129372422</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474177</v>
+        <v>474226</v>
       </c>
       <c r="R21" t="n">
-        <v>6920810</v>
+        <v>6920695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372432</v>
+        <v>129372421</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474398</v>
+        <v>474223</v>
       </c>
       <c r="R22" t="n">
-        <v>6921134</v>
+        <v>6920680</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372421</v>
+        <v>129372432</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474223</v>
+        <v>474398</v>
       </c>
       <c r="R23" t="n">
-        <v>6920680</v>
+        <v>6921134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
         <v>129372426</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129372418</v>
+        <v>129372447</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474395</v>
+        <v>474144</v>
       </c>
       <c r="R2" t="n">
-        <v>6921132</v>
+        <v>6920595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129372447</v>
+        <v>129372417</v>
       </c>
       <c r="B3" t="n">
-        <v>91589</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474144</v>
+        <v>474246</v>
       </c>
       <c r="R3" t="n">
-        <v>6920595</v>
+        <v>6920927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129372443</v>
+        <v>129372418</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>92632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474197</v>
+        <v>474395</v>
       </c>
       <c r="R4" t="n">
-        <v>6920850</v>
+        <v>6921132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129372417</v>
+        <v>129372436</v>
       </c>
       <c r="B5" t="n">
-        <v>92311</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474246</v>
+        <v>474140</v>
       </c>
       <c r="R5" t="n">
-        <v>6920927</v>
+        <v>6920856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129372433</v>
+        <v>129372437</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474231</v>
+        <v>474157</v>
       </c>
       <c r="R6" t="n">
-        <v>6920694</v>
+        <v>6920662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,51 +1160,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129372439</v>
+        <v>129372438</v>
       </c>
       <c r="B7" t="n">
-        <v>57840</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
@@ -1227,7 +1198,7 @@
         <v>474241</v>
       </c>
       <c r="R7" t="n">
-        <v>6920840</v>
+        <v>6920718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,61 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129372446</v>
+        <v>129372419</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474291</v>
+        <v>474177</v>
       </c>
       <c r="R8" t="n">
-        <v>6920735</v>
+        <v>6920810</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1332,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,7 +1341,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129372436</v>
+        <v>129372420</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474140</v>
+        <v>474211</v>
       </c>
       <c r="R9" t="n">
-        <v>6920856</v>
+        <v>6920575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1502,61 +1461,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129372442</v>
+        <v>129372421</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474194</v>
+        <v>474223</v>
       </c>
       <c r="R10" t="n">
-        <v>6920828</v>
+        <v>6920680</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1536,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,7 +1545,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,61 +1563,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129372444</v>
+        <v>129372422</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474195</v>
+        <v>474226</v>
       </c>
       <c r="R11" t="n">
-        <v>6920866</v>
+        <v>6920695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1638,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,7 +1647,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1740,32 +1665,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129372445</v>
+        <v>129372423</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474362</v>
+        <v>474265</v>
       </c>
       <c r="R12" t="n">
-        <v>6920913</v>
+        <v>6920708</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1736,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,32 +1767,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129372441</v>
+        <v>129372424</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474236</v>
+        <v>474312</v>
       </c>
       <c r="R13" t="n">
-        <v>6920883</v>
+        <v>6920684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1838,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129372438</v>
+        <v>129372425</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474241</v>
+        <v>474348</v>
       </c>
       <c r="R14" t="n">
-        <v>6920718</v>
+        <v>6920993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129372437</v>
+        <v>129372426</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474157</v>
+        <v>474347</v>
       </c>
       <c r="R15" t="n">
-        <v>6920662</v>
+        <v>6921012</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,6 +2042,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129372424</v>
+        <v>129372427</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474312</v>
+        <v>474400</v>
       </c>
       <c r="R16" t="n">
-        <v>6920684</v>
+        <v>6921157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129372420</v>
+        <v>129372428</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474211</v>
+        <v>474409</v>
       </c>
       <c r="R17" t="n">
-        <v>6920575</v>
+        <v>6921139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,7 +2250,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129372423</v>
+        <v>129372429</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474265</v>
+        <v>474426</v>
       </c>
       <c r="R18" t="n">
-        <v>6920708</v>
+        <v>6921125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129372425</v>
+        <v>129372430</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474348</v>
+        <v>474422</v>
       </c>
       <c r="R19" t="n">
-        <v>6920993</v>
+        <v>6921095</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129372419</v>
+        <v>129372431</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474177</v>
+        <v>474420</v>
       </c>
       <c r="R20" t="n">
-        <v>6920810</v>
+        <v>6921094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2611,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129372422</v>
+        <v>129372432</v>
       </c>
       <c r="B21" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474226</v>
+        <v>474398</v>
       </c>
       <c r="R21" t="n">
-        <v>6920695</v>
+        <v>6921134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372421</v>
+        <v>129372433</v>
       </c>
       <c r="B22" t="n">
-        <v>57740</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,34 +2696,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474223</v>
+        <v>474231</v>
       </c>
       <c r="R22" t="n">
-        <v>6920680</v>
+        <v>6920694</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2768,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Några styckna</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,10 +2795,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372432</v>
+        <v>129372439</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>58057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,16 +2806,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2870,17 +2823,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474398</v>
+        <v>474241</v>
       </c>
       <c r="R23" t="n">
-        <v>6921134</v>
+        <v>6920840</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2913,11 +2882,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,32 +2908,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129372426</v>
+        <v>129372441</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2943,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474347</v>
+        <v>474236</v>
       </c>
       <c r="R24" t="n">
-        <v>6921012</v>
+        <v>6920883</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3017,11 +2981,6 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3043,6 +3002,557 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129372442</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>474194</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6920828</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129372443</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>474197</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6920850</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129372444</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>474195</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6920866</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129372445</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>474362</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6920913</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129372446</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>474291</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6920735</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372418</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372436</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372437</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372419</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372420</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372421</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372422</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372423</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372424</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372425</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372426</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372427</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,6 +2354,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372428</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372429</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372430</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372431</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372432</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2792,6 +2897,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372433</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372439</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3002,6 +3117,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372441</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3121,6 +3241,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372442</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3218,6 +3343,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372443</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3337,6 +3467,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372444</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3434,6 +3569,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372445</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3553,8 +3693,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372433</v>
+        <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>58114</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2801,42 +2801,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bryngelhögen nö, Jmt</t>
+          <t>Norrbodstugan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474231</v>
+        <v>474179</v>
       </c>
       <c r="R22" t="n">
-        <v>6920694</v>
+        <v>6920958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,17 +2860,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Några styckna</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,16 +2906,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372433</t>
+          <t>https://artportalen.se/Sighting/136189278</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129372439</v>
+        <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2933,33 +2940,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bryngelhögen nö, Jmt</t>
+          <t>Norrbodstugan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474241</v>
+        <v>474185</v>
       </c>
       <c r="R23" t="n">
-        <v>6920840</v>
+        <v>6920953</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,12 +2977,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,51 +3023,59 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372439</t>
+          <t>https://artportalen.se/Sighting/136189279</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129372441</v>
+        <v>129372433</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bryngelhögen nö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474236</v>
+        <v>474231</v>
       </c>
       <c r="R24" t="n">
-        <v>6920883</v>
+        <v>6920694</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,6 +3110,11 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Några styckna</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3119,52 +3138,52 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372441</t>
+          <t>https://artportalen.se/Sighting/129372433</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129372442</v>
+        <v>129372439</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>58057</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3176,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474194</v>
+        <v>474241</v>
       </c>
       <c r="R25" t="n">
-        <v>6920828</v>
+        <v>6920840</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3214,18 +3233,12 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3243,13 +3256,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372442</t>
+          <t>https://artportalen.se/Sighting/129372439</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129372443</v>
+        <v>129372441</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3284,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474197</v>
+        <v>474236</v>
       </c>
       <c r="R26" t="n">
-        <v>6920850</v>
+        <v>6920883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,13 +3358,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372443</t>
+          <t>https://artportalen.se/Sighting/129372441</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129372444</v>
+        <v>129372442</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3381,7 +3394,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3402,10 +3415,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474195</v>
+        <v>474194</v>
       </c>
       <c r="R27" t="n">
-        <v>6920866</v>
+        <v>6920828</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3455,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3469,13 +3482,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372444</t>
+          <t>https://artportalen.se/Sighting/129372442</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129372445</v>
+        <v>129372443</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3510,10 +3523,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474362</v>
+        <v>474197</v>
       </c>
       <c r="R28" t="n">
-        <v>6920913</v>
+        <v>6920850</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,13 +3584,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129372445</t>
+          <t>https://artportalen.se/Sighting/129372443</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129372446</v>
+        <v>129372444</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3628,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474291</v>
+        <v>474195</v>
       </c>
       <c r="R29" t="n">
-        <v>6920735</v>
+        <v>6920866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3694,6 +3707,232 @@
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372444</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129372445</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>474362</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6920913</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372445</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129372446</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bryngelhögen nö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>474291</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6920735</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129372446</t>
         </is>
@@ -3729,6 +3968,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2793,7 +2793,7 @@
         <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2793,7 +2793,7 @@
         <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2793,7 +2793,7 @@
         <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2793,7 +2793,7 @@
         <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2793,7 +2793,7 @@
         <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
